--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartAndImage/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartAndImage/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re76bc7772ca54414"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfa9efff397534a2a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0e00fd75486040fd"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6a328bcedb054f28"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -165,7 +165,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rea15b339d06944e0"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rb91618e2852d44bf"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -213,6 +213,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80235b04453a4edb"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1282cfc5f76643c8"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartAndImage/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartAndImage/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfa9efff397534a2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R029af13abd8b4507"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6a328bcedb054f28"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra05e100032984c31"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -165,7 +165,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rb91618e2852d44bf"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rb7317208c57e4b02"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -213,6 +213,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1282cfc5f76643c8"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf45d2febdc2e418f"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartAndImage/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartAndImage/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R029af13abd8b4507"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7afb78365b8c416e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra05e100032984c31"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R675fc22cdca1448d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -165,7 +165,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rb7317208c57e4b02"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Ra588d22a7da44d67"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -213,6 +213,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf45d2febdc2e418f"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0dbb45ccf3d54afe"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartAndImage/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartAndImage/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7afb78365b8c416e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb6bf5420ce0c46b4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R675fc22cdca1448d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R178b5ff0c2c944e1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -165,7 +165,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Ra588d22a7da44d67"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rf5a0c65863504131"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -213,6 +213,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0dbb45ccf3d54afe"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b82f663b0654f40"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartAndImage/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartAndImage/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb6bf5420ce0c46b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R86b26d7664e64cae"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R178b5ff0c2c944e1"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R06825ab098c54133"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -165,7 +165,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rf5a0c65863504131"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R70ca5c5b6ca945a7"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -213,6 +213,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b82f663b0654f40"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb4002d4870549ed"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartAndImage/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartAndImage/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R86b26d7664e64cae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5f1ae80b4ed64497"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R06825ab098c54133"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5807d907fec54e33"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -165,7 +165,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R70ca5c5b6ca945a7"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R45462562f4bf43d5"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -213,6 +213,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb4002d4870549ed"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48d39c58aae34e68"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartAndImage/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartAndImage/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5f1ae80b4ed64497"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R65d17c56ff124d5e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5807d907fec54e33"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3896d72cb1d54bdf"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -165,7 +165,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R45462562f4bf43d5"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rd55da1d776894d14"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -213,6 +213,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48d39c58aae34e68"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e47b6b085d94665"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartAndImage/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartAndImage/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R65d17c56ff124d5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R98f8909fcc2849a2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3896d72cb1d54bdf"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdb8545501db84f37"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -165,7 +165,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rd55da1d776894d14"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rd308e7f6cf8542c9"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -213,6 +213,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e47b6b085d94665"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1607d72ffe714092"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartAndImage/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartAndImage/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R98f8909fcc2849a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re3f4649844b645fe"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdb8545501db84f37"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3f3ff0f86e1d4b91"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -165,7 +165,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rd308e7f6cf8542c9"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R7c53fbe1afa241c7"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -213,6 +213,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1607d72ffe714092"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10d3c187e96043e2"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartAndImage/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartAndImage/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re3f4649844b645fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1a9fafd2ad7948ce"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3f3ff0f86e1d4b91"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re06c2c22628e42d9"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -165,7 +165,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R7c53fbe1afa241c7"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rbe61b6bd4c384458"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -213,6 +213,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10d3c187e96043e2"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcdb1386134124137"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartAndImage/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartAndImage/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1a9fafd2ad7948ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfad8f8fabd0142e1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re06c2c22628e42d9"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R355c65c2599348f6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -165,7 +165,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rbe61b6bd4c384458"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rb8f4d6f492b148ac"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -213,6 +213,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcdb1386134124137"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7f58f2aa19e4a49"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartAndImage/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartAndImage/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfad8f8fabd0142e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdbcb3649ca5b42fa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R355c65c2599348f6"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra360b52de3f344ce"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -165,7 +165,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rb8f4d6f492b148ac"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rf61b3a7d665548a9"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -213,6 +213,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7f58f2aa19e4a49"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re48b0c10509b4995"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartAndImage/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartAndImage/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdbcb3649ca5b42fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd8f387742ed8406f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra360b52de3f344ce"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R07ec99b3b4a749ee"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -165,7 +165,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rf61b3a7d665548a9"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rcb95a668e0044e86"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -213,6 +213,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re48b0c10509b4995"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ba265afdfba40a7"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartAndImage/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartAndImage/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd8f387742ed8406f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf2b90c07dd66487e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R07ec99b3b4a749ee"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5f27569189a04260"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -165,7 +165,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rcb95a668e0044e86"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Reb57d0f61793472f"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -213,6 +213,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ba265afdfba40a7"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdfc11ee5b1924021"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartAndImage/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartAndImage/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf2b90c07dd66487e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R35a14d3aa51540c8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5f27569189a04260"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R43ed085677584480"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -165,7 +165,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Reb57d0f61793472f"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R51d28d1ebcff4fe2"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -213,6 +213,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdfc11ee5b1924021"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43978ecdfc204205"/>
 </x:worksheet>
 </file>